--- a/_downloads/6038d644f51b8af36e528d6ce0f7621a/2. Coberturas con Futuros.xlsx
+++ b/_downloads/6038d644f51b8af36e528d6ce0f7621a/2. Coberturas con Futuros.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23901"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\migue\Dropbox\UNAL\DERIVADOS FINANCIEROS\CLASES\Futuros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBC0E92-D34C-4EB8-B4CB-3AC47360523F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B92D1F-149C-40AC-BC52-5CA896CF722C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{88DCEA8C-2315-4153-90C9-3DDE4F46E6CC}"/>
   </bookViews>
@@ -18,13 +18,13 @@
     <sheet name="Cobertura portafolios" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="F0">'Razón cobertura 100%'!$C$9</definedName>
-    <definedName name="FT">'Razón cobertura 100%'!$C$15</definedName>
-    <definedName name="K">'Razón cobertura 100%'!$C$10</definedName>
-    <definedName name="QForward">'Razón cobertura 100%'!$C$9</definedName>
-    <definedName name="Qfuturos">'Razón cobertura 100%'!$C$8</definedName>
-    <definedName name="Qsubyacente">'Razón cobertura 100%'!$C$2</definedName>
-    <definedName name="ST">'Razón cobertura 100%'!$C$16</definedName>
+    <definedName name="F0">'Razón cobertura 100%'!$B$9</definedName>
+    <definedName name="FT">'Razón cobertura 100%'!$B$15</definedName>
+    <definedName name="K">'Razón cobertura 100%'!$B$10</definedName>
+    <definedName name="QForward">'Razón cobertura 100%'!$B$9</definedName>
+    <definedName name="Qfuturos">'Razón cobertura 100%'!$B$8</definedName>
+    <definedName name="Qsubyacente">'Razón cobertura 100%'!$B$2</definedName>
+    <definedName name="ST">'Razón cobertura 100%'!$B$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -101,9 +101,6 @@
     <t>Razón cobertura</t>
   </si>
   <si>
-    <t>Forward</t>
-  </si>
-  <si>
     <t>Activo subyacente</t>
   </si>
   <si>
@@ -162,21 +159,6 @@
   </si>
   <si>
     <t>Precio con cobertura</t>
-  </si>
-  <si>
-    <r>
-      <t>Q</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t>futuros</t>
-    </r>
   </si>
   <si>
     <r>
@@ -300,30 +282,6 @@
     <t>Al vencimiento</t>
   </si>
   <si>
-    <r>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (futuro V)</t>
-    </r>
-  </si>
-  <si>
     <t>El día de hoy (agosto), un exportador tiene proyectado vender en la cuarta semana de septiembre 215.000 USD al precio spot.
 Realiza cobertura solo con futuros TRM con una razón de cobertura lo más aproximada al 100%.</t>
   </si>
@@ -357,9 +315,6 @@
   </si>
   <si>
     <t>Beta portafolio</t>
-  </si>
-  <si>
-    <t>Futuro COLCAP</t>
   </si>
   <si>
     <t>Portafolio de inversión</t>
@@ -470,6 +425,51 @@
       </rPr>
       <t>objetivo</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Futuro V)</t>
+    </r>
+  </si>
+  <si>
+    <t>Futuro COS</t>
+  </si>
+  <si>
+    <r>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>Futuros</t>
+    </r>
+  </si>
+  <si>
+    <t>Futuro</t>
   </si>
 </sst>
 </file>
@@ -706,7 +706,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -823,6 +823,14 @@
     <xf numFmtId="6" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -874,13 +882,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>713014</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>55150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>618160</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>667146</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>48500</xdr:rowOff>
     </xdr:to>
@@ -918,18 +926,18 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>114299</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>50692</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>235047</xdr:colOff>
       <xdr:row>53</xdr:row>
       <xdr:rowOff>165917</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="CuadroTexto 8">
@@ -1494,7 +1502,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="CuadroTexto 8">
@@ -1817,13 +1825,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>16328</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>43897</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>15395</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>172596</xdr:rowOff>
@@ -1862,18 +1870,18 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>326571</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>146958</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>253090</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>71683</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="CuadroTexto 7">
@@ -2438,7 +2446,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="CuadroTexto 7">
@@ -2745,13 +2753,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>168728</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>110289</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>511629</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>169926</xdr:rowOff>
@@ -2789,19 +2797,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>5443</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>103414</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>713799</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>28139</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="CuadroTexto 5">
@@ -3391,7 +3399,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="CuadroTexto 5">
@@ -3748,13 +3756,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>326277</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>146956</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>525167</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>152401</xdr:rowOff>
@@ -3792,19 +3800,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>5442</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>16329</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>33551</xdr:colOff>
       <xdr:row>53</xdr:row>
       <xdr:rowOff>131554</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="CuadroTexto 6">
@@ -4376,7 +4384,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="CuadroTexto 6">
@@ -4722,6 +4730,3057 @@
                 <a:t>"  </a:t>
               </a:r>
               <a:endParaRPr lang="es-CO" sz="800">
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>195943</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>182337</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1632178" cy="195118"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="CuadroTexto 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A197EDBD-D1C3-47CD-93CE-FFFF5FDC2998}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4054929" y="1352551"/>
+              <a:ext cx="1632178" cy="195118"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-CO" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Q</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>F</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Q</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>S</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>×</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>Raz</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>ó</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>n</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>cobertura</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="es-CO" sz="1100">
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="CuadroTexto 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A197EDBD-D1C3-47CD-93CE-FFFF5FDC2998}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4054929" y="1352551"/>
+              <a:ext cx="1632178" cy="195118"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"Q</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" _</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>F</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> "=" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"Q</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" _"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>S</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"  "×Razón cobertura</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"</a:t>
+              </a:r>
+              <a:endParaRPr lang="es-CO" sz="1100">
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>70757</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>130629</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>799167</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123257</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E5E77BC-E1A4-43CF-8B68-4C8262E8A842}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="832757" y="7184572"/>
+          <a:ext cx="3858053" cy="890699"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>179615</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>146957</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>636816</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>70523</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{237B0230-39ED-4E0E-8E6F-44DD95D0ABD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5807529" y="7200900"/>
+          <a:ext cx="3630386" cy="821637"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>141515</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>100693</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1379801" cy="382990"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="CuadroTexto 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BA19D76-4C51-4D6C-B93B-A14A17B57269}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4245429" y="4269922"/>
+              <a:ext cx="1379801" cy="382990"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>Raz</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>ó</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>n</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>cobertura</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>Q</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>F</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:num>
+                      <m:den>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>Q</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>A</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="es-CO" sz="1100">
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="CuadroTexto 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BA19D76-4C51-4D6C-B93B-A14A17B57269}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4245429" y="4269922"/>
+              <a:ext cx="1379801" cy="382990"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"Razón cobertura=" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> "</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>Q</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" _"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>F</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" /"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>Q</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" _"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>A</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"  </a:t>
+              </a:r>
+              <a:endParaRPr lang="es-CO" sz="1100">
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>424543</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>193221</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1634101" cy="195566"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="CuadroTexto 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4E7F1B0-4146-4AD2-9877-FF0F1B56CE9E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4376057" y="1847850"/>
+              <a:ext cx="1634101" cy="195566"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-CO" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>V</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>F</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>F</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>0</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>×</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>Tama</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>ñ</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>o</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>contrato</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="es-CO" sz="1100">
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="CuadroTexto 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4E7F1B0-4146-4AD2-9877-FF0F1B56CE9E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4376057" y="1847850"/>
+              <a:ext cx="1634101" cy="195566"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"V</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" _</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>F</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> "=" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"F</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" _"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>0</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"  "×Tamaño contrato</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"</a:t>
+              </a:r>
+              <a:endParaRPr lang="es-CO" sz="1100">
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>16329</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>24494</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2598340" cy="200568"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="CuadroTexto 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{913D2A16-1CA4-4BF8-9F75-975F76A296C3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3967843" y="3268437"/>
+              <a:ext cx="2598340" cy="200568"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>Comp</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>.=</m:t>
+                    </m:r>
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>F</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>0</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−</m:t>
+                        </m:r>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>F</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>T</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:d>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>×</m:t>
+                    </m:r>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>N</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>∗</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>×</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>Tama</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>ñ</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>o</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>contrato</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="es-CO" sz="1100">
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="CuadroTexto 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{913D2A16-1CA4-4BF8-9F75-975F76A296C3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3967843" y="3268437"/>
+              <a:ext cx="2598340" cy="200568"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"Comp.=" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>("</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>F</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" _"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>0</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"  "</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>−</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>" "</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>F</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" _"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>T</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"  )"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>×</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"N</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" ^"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>∗</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"  "</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>×Tamaño contrato</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"</a:t>
+              </a:r>
+              <a:endParaRPr lang="es-CO" sz="1100">
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>941615</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>857476</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>97843</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="CuadroTexto 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B8E2E48-5CE4-4EF2-A5A4-2B4BA106DC65}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3940629" y="2204356"/>
+              <a:ext cx="868361" cy="380873"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="es-CO"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-CO" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>N</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>∗</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>β</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-CO" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="es-CO" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>V</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>A</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:num>
+                      <m:den>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="es-CO" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>V</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>F</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="es-CO" sz="1100">
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="CuadroTexto 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B8E2E48-5CE4-4EF2-A5A4-2B4BA106DC65}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3940629" y="2204356"/>
+              <a:ext cx="868361" cy="380873"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="es-CO"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"N</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" ^"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>∗</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> "</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>=</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>β" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> "</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>V</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" _"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>A</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" /"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>V</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" _"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>F</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"  </a:t>
+              </a:r>
+              <a:endParaRPr lang="es-CO" sz="1100">
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>446313</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>130628</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>727662</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>114172</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="CuadroTexto 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A531A00C-AE7A-4649-A20C-120D9489B523}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5350327" y="2220685"/>
+              <a:ext cx="1233849" cy="380873"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="es-CO"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-CO" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>N</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>∗</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>(</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>β</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>−</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-CO" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>β</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>∗</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>)</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-CO" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="es-CO" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>V</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>A</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:num>
+                      <m:den>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="es-CO" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>V</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <m:rPr>
+                                <m:nor/>
+                              </m:rPr>
+                              <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                              </a:rPr>
+                              <m:t>F</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="es-CO" sz="1100">
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="CuadroTexto 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A531A00C-AE7A-4649-A20C-120D9489B523}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5350327" y="2220685"/>
+              <a:ext cx="1233849" cy="380873"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="es-CO"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"N</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" ^"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>∗</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> "</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>=</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>(β</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>−</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"β</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>^"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>∗</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"  ")</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> "</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>V</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>_"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>A</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>/"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>V</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>_"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>F</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"  </a:t>
+              </a:r>
+              <a:endParaRPr lang="es-CO" sz="1100">
                 <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
@@ -5033,603 +8092,665 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87D8E4D-9735-47C3-AC92-B3288919FDE3}">
-  <dimension ref="B1:H41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.42578125" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" customWidth="1"/>
+    <col min="7" max="7" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="50" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="50" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="52"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="56"/>
     </row>
-    <row r="2" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="B2" s="3">
         <v>150000</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="3">
         <v>150000</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="5">
+      <c r="B3" s="5">
         <v>185</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="2" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="5">
+      <c r="H3" s="5">
         <v>185</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7">
+      <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="6" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="7">
+      <c r="H4" s="7">
         <v>1</v>
       </c>
-      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="1"/>
-      <c r="C5" s="5"/>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="50" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="55"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="55"/>
+      <c r="I6" s="56"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="50" t="s">
+      <c r="B7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="51"/>
-      <c r="H6" s="52"/>
+      <c r="H7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="4"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
+    <row r="8" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="3">
+        <f>+B4*B2</f>
+        <v>150000</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" s="3">
+        <f>+H4*H2</f>
+        <v>150000</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="9">
+        <v>3450</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="2" t="s">
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="9">
+        <v>3450</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3">
-        <f>+C4*C2</f>
-        <v>150000</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="3">
-        <f>+G4*G2</f>
-        <v>150000</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>3</v>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5">
+        <v>185</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="5">
+        <v>185</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="9">
-        <v>3450</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="9">
-        <v>3450</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>9</v>
-      </c>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="8"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="5">
-        <v>185</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="5">
-        <v>185</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="8"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="1"/>
-      <c r="C12" s="5"/>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="50" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="55"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="55"/>
+      <c r="I13" s="56"/>
+    </row>
+    <row r="14" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="50" t="s">
+      <c r="B14" s="9">
+        <v>3300</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="51"/>
-      <c r="H13" s="52"/>
+      <c r="H14" s="9">
+        <v>3300</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="14" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+    <row r="15" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="9">
+        <v>3350</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="9">
+        <v>3350</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="9">
-        <v>3300</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="9">
-        <v>3300</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>9</v>
+      <c r="B17" s="9">
+        <f>+B14*B2</f>
+        <v>495000000</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="9">
+        <f>-H14*H2</f>
+        <v>-495000000</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="9">
-        <v>3350</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="9">
-        <v>3350</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="2"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="9">
-        <f>+C14*C2</f>
-        <v>495000000</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="2" t="s">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="9">
-        <f>-G14*G2</f>
-        <v>-495000000</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="9">
+      <c r="B18" s="9">
         <f>+(F0-FT)*Qfuturos</f>
         <v>15000000</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="2" t="s">
+      <c r="C18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="9">
+        <f>+(H15-H9)*H8</f>
+        <v>-15000000</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="9">
-        <f>+(G15-G9)*G8</f>
-        <v>-15000000</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>9</v>
+      <c r="B19" s="12">
+        <f>SUM(B17:B18)</f>
+        <v>510000000</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="12">
+        <f>SUM(H17:H18)</f>
+        <v>-510000000</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="12">
-        <f>SUM(C17:C18)</f>
-        <v>510000000</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="11" t="s">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="4"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="12">
-        <f>SUM(G17:G18)</f>
-        <v>-510000000</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>9</v>
+      <c r="B21" s="18">
+        <f>+B19/Qsubyacente</f>
+        <v>3400</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="18">
+        <f>-H19/Qsubyacente</f>
+        <v>3400</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="2"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="4"/>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="8"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="18">
-        <f>+C19/Qsubyacente</f>
-        <v>3400</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="18">
-        <f>-G19/Qsubyacente</f>
-        <v>3400</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>9</v>
-      </c>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="55"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" s="55"/>
+      <c r="I31" s="56"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="6"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="8"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="51"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="G31" s="51"/>
-      <c r="H31" s="52"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="21">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="21">
         <f>Qfuturos*F0*0.3%</f>
         <v>1552500</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="23"/>
-      <c r="F32" s="2" t="s">
+      <c r="C32" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" s="21">
+        <f>H8*H9*0.3%</f>
+        <v>1552500</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="21">
+        <f>+B32*19%</f>
+        <v>294975</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="21">
+        <f>+H32*19%</f>
+        <v>294975</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G32" s="21">
-        <f>15000+G8*G9*0.3%</f>
-        <v>1567500</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" s="21">
-        <f>+C32*19%</f>
-        <v>294975</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="23"/>
-      <c r="F33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G33" s="21">
-        <f>+G32*19%</f>
-        <v>297825</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34" s="21">
+      <c r="B34" s="21">
         <f>Qfuturos*FT*0.3%</f>
         <v>1507500</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="23"/>
-      <c r="F34" s="2" t="s">
+      <c r="C34" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H34" s="21">
+        <f>H8*H15*0.3%</f>
+        <v>1507500</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="21">
+        <f>+B34*19%</f>
+        <v>286425</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H35" s="21">
+        <f>+H34*19%</f>
+        <v>286425</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G34" s="21">
-        <f>15000+G8*G15*0.3%</f>
-        <v>1522500</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>9</v>
+      <c r="B36" s="22">
+        <f>SUM(B32:B35)</f>
+        <v>3641400</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H36" s="22">
+        <f>SUM(H32:H35)</f>
+        <v>3641400</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="27"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="26"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="21">
-        <f>+C34*19%</f>
-        <v>286425</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="23"/>
-      <c r="F35" s="2" t="s">
+      <c r="B38" s="21">
+        <f>+B19-B36</f>
+        <v>506358600</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G35" s="21">
-        <f>+G34*19%</f>
-        <v>289275</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>9</v>
+      <c r="H38" s="21">
+        <f>+H19-H36</f>
+        <v>-513641400</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="11" t="s">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="27"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="26"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C36" s="22">
-        <f>SUM(C32:C35)</f>
-        <v>3641400</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="23"/>
-      <c r="F36" s="11" t="s">
+      <c r="B40" s="30">
+        <f>+B38/Qsubyacente</f>
+        <v>3375.7240000000002</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="G36" s="22">
-        <f>SUM(G32:G35)</f>
-        <v>3677100</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>9</v>
+      <c r="H40" s="30">
+        <f>-H38/Qsubyacente</f>
+        <v>3424.2759999999998</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="27"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="26"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="21">
-        <f>+C19-C36</f>
-        <v>506358600</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="23"/>
-      <c r="F38" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G38" s="21">
-        <f>+G19-G36</f>
-        <v>-513677100</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="27"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="26"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="30">
-        <f>+C38/Qsubyacente</f>
-        <v>3375.7240000000002</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="23"/>
-      <c r="F40" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="G40" s="30">
-        <f>-G38/Qsubyacente</f>
-        <v>3424.5140000000001</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="23"/>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
       <c r="D41" s="23"/>
       <c r="E41" s="23"/>
       <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="G13:I13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="G34 C34" formula="1"/>
-  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -5639,10 +8760,9 @@
   <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="1" customWidth="1"/>
+    <col min="3" max="4" width="14.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" style="1"/>
     <col min="6" max="6" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -5651,54 +8771,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B1" s="57" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="F1" s="57" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="50"/>
+      <c r="F1" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B2" s="58" t="s">
+      <c r="A2" s="62" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="51"/>
+      <c r="F2" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="F2" s="58" t="s">
-        <v>57</v>
-      </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="51"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="51"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
+      <c r="A5" s="62"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="51"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="40"/>
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
       <c r="D6" s="40"/>
@@ -5707,18 +8833,17 @@
       <c r="H6" s="40"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="5"/>
-      <c r="B7" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="31">
+      <c r="A7" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="31">
         <v>215000</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="31">
         <v>215000</v>
@@ -5728,29 +8853,31 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="54" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="56"/>
-      <c r="F9" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9" s="55"/>
-      <c r="H9" s="56"/>
+      <c r="A9" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="59"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="16"/>
+      <c r="F9" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="59"/>
+      <c r="H9" s="60"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="42">
+      <c r="A10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="42">
         <v>50000</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="D10" s="20"/>
       <c r="F10" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G10" s="42">
         <v>5000</v>
@@ -5760,178 +8887,184 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="32">
+      <c r="A11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="32">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="C11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="20"/>
       <c r="F11" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G11" s="32">
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="4"/>
+      <c r="A12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="20"/>
       <c r="F12" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="8"/>
+      <c r="A13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="20"/>
       <c r="F13" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H13" s="8"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B15" s="53" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="53"/>
-      <c r="F15" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" s="53"/>
+      <c r="A15" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="57"/>
+      <c r="F15" s="57" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="57"/>
     </row>
     <row r="16" spans="1:8" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A16" s="34" t="s">
+        <v>34</v>
+      </c>
       <c r="B16" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="36">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="36">
         <v>3651</v>
       </c>
       <c r="F17" s="35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G17" s="36">
         <v>3654.2</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="36">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="36">
         <v>3670.15</v>
       </c>
       <c r="F18" s="35" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G18" s="36">
         <v>3671.22</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B19" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="36">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="36">
         <v>3681.9</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G19" s="36">
         <v>3681.51</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B20" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="36">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="36">
         <v>3698.5</v>
       </c>
       <c r="F20" s="35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G20" s="36">
         <v>3699.74</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B22" s="54" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="55"/>
-      <c r="D22" s="56"/>
-      <c r="F22" s="54" t="s">
-        <v>50</v>
-      </c>
-      <c r="G22" s="55"/>
-      <c r="H22" s="56"/>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="58" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="59"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="16"/>
+      <c r="F22" s="58" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="59"/>
+      <c r="H22" s="60"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="38">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="38">
         <v>4</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="20"/>
       <c r="F23" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G23" s="38">
         <v>43</v>
       </c>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="31">
-        <f>+C23*C10</f>
+    <row r="24" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="31">
+        <f>+B23*B10</f>
         <v>200000</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="D24" s="20"/>
       <c r="F24" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="G24" s="31">
         <f>+G23*G10</f>
@@ -5941,17 +9074,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="43">
-        <f>+C24/C7</f>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="43">
+        <f>+B24/B7</f>
         <v>0.93023255813953487</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="20"/>
       <c r="F25" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G25" s="43">
         <f>+G24/G7</f>
@@ -5959,204 +9093,216 @@
       </c>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="39">
-        <f>+C20</f>
+    <row r="26" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="39">
+        <f>+B20</f>
         <v>3698.5</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="C26" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="20"/>
       <c r="F26" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G26" s="39">
         <f>+G20</f>
         <v>3699.74</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="41" t="s">
+    <row r="27" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="20"/>
+      <c r="F27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="41" t="s">
         <v>13</v>
-      </c>
-      <c r="D27" s="8"/>
-      <c r="F27" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G27" s="41" t="s">
-        <v>14</v>
       </c>
       <c r="H27" s="8"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B29" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="52"/>
-      <c r="F29" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G29" s="51"/>
-      <c r="H29" s="52"/>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="55"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="16"/>
+      <c r="F29" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29" s="55"/>
+      <c r="H29" s="56"/>
     </row>
-    <row r="30" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" s="39">
+    <row r="30" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="39">
         <v>3420</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="C30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="20"/>
       <c r="F30" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G30" s="39">
         <v>3420</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B31" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="39">
+    <row r="31" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="39">
         <v>3415.25</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="C31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="20"/>
       <c r="F31" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="G31" s="39">
         <v>3428.85</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B32" s="2"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="4"/>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="2"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="20"/>
       <c r="F32" s="2"/>
       <c r="G32" s="20"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="21">
+        <f>+B30*B7</f>
+        <v>735300000</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="20"/>
+      <c r="F33" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C33" s="21">
-        <f>+C30*C7</f>
-        <v>735300000</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="G33" s="21">
         <f>-G30*G7</f>
         <v>-735300000</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B34" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" s="21">
-        <f>+(C26-C31)*C24</f>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="21">
+        <f>+(B26-B31)*B24</f>
         <v>56650000</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="C34" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="20"/>
       <c r="F34" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G34" s="21">
         <f>+(G31-G26)*G24</f>
         <v>-58241349.99999997</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B35" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="22">
-        <f>SUM(C33:C34)</f>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="22">
+        <f>SUM(B33:B34)</f>
         <v>791950000</v>
       </c>
-      <c r="D35" s="13" t="s">
-        <v>9</v>
-      </c>
+      <c r="C35" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="52"/>
       <c r="F35" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G35" s="22">
         <f>SUM(G33:G34)</f>
         <v>-793541350</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B36" s="2"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="4"/>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="2"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="20"/>
       <c r="F36" s="2"/>
       <c r="G36" s="20"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B37" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="24">
-        <f>+C35/C7</f>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="24">
+        <f>+B35/B7</f>
         <v>3683.4883720930234</v>
       </c>
-      <c r="D37" s="19" t="s">
-        <v>9</v>
-      </c>
+      <c r="C37" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="53"/>
       <c r="F37" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G37" s="24">
         <f>-G35/G7</f>
         <v>3690.89</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B38" s="6"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="8"/>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="6"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="20"/>
       <c r="F38" s="6"/>
       <c r="G38" s="33"/>
       <c r="H38" s="8"/>
@@ -6166,333 +9312,376 @@
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="F22:H22"/>
     <mergeCell ref="F29:H29"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C5"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="F2:H5"/>
     <mergeCell ref="F9:H9"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A29:C29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98A3303D-9E49-43CD-B485-BDB180602A77}">
-  <dimension ref="B1:H23"/>
+  <dimension ref="B1:J23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="1"/>
     <col min="2" max="2" width="17" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="1"/>
-    <col min="6" max="6" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="11.42578125" style="1"/>
+    <col min="5" max="6" width="14.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="1"/>
+    <col min="8" max="8" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B1" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="52"/>
-      <c r="F1" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="52"/>
+    <row r="1" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B1" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="55"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="H1" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="55"/>
+      <c r="J1" s="56"/>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C2" s="21">
-        <v>3000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="21">
-        <v>3000000000</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="H2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="21">
+        <v>2000000000</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C3" s="15">
         <v>1.2</v>
       </c>
       <c r="D3" s="8"/>
-      <c r="F3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="15">
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="H3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" s="15">
         <v>1.2</v>
       </c>
-      <c r="H3" s="8"/>
+      <c r="J3" s="8"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="52"/>
-      <c r="F5" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="51"/>
-      <c r="H5" s="52"/>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B5" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="55"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="H5" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="55"/>
+      <c r="J5" s="56"/>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" s="21">
-        <v>25000</v>
+        <v>2500</v>
       </c>
       <c r="D6" s="4"/>
-      <c r="F6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="21">
-        <v>25000</v>
-      </c>
-      <c r="H6" s="4"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="H6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="21">
+        <v>2500</v>
+      </c>
+      <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7" s="45">
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="45">
+        <v>43</v>
+      </c>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="H7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="45">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>45</v>
+      <c r="J7" s="4" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="44">
         <v>1131</v>
       </c>
       <c r="D8" s="8"/>
-      <c r="F8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="44">
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="H8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="44">
         <v>1131</v>
       </c>
-      <c r="H8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B10" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="52"/>
-      <c r="F10" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="51"/>
-      <c r="H10" s="52"/>
+    <row r="10" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B10" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="55"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="H10" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="55"/>
+      <c r="J10" s="56"/>
     </row>
-    <row r="11" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C11" s="21">
         <f>+C8*C6</f>
-        <v>28275000</v>
+        <v>2827500</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="16">
+        <v>64</v>
+      </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="H11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" s="16">
         <v>0.5</v>
       </c>
-      <c r="H11" s="17"/>
+      <c r="J11" s="17"/>
     </row>
-    <row r="12" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="46">
-        <f>+C2/C11</f>
-        <v>106.10079575596816</v>
+        <v>65</v>
+      </c>
+      <c r="C12" s="25">
+        <f>+C3*C2/C11</f>
+        <v>848.80636604774531</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="F12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="21">
-        <f>+G8*G6</f>
-        <v>28275000</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>68</v>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="H12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" s="21">
+        <f>+I8*I6</f>
+        <v>2827500</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C13" s="25">
         <f>+ROUND(C12,)</f>
-        <v>106</v>
+        <v>849</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="46">
-        <f>+(G3-G11)*G2/G12</f>
-        <v>74.270557029177709</v>
-      </c>
-      <c r="H13" s="4"/>
+        <v>66</v>
+      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="H13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="46">
+        <f>+(I3-I11)*I2/I12</f>
+        <v>495.13704686118479</v>
+      </c>
+      <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" s="8"/>
-      <c r="F14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="25">
-        <f>+ROUND(G13,)</f>
-        <v>74</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>70</v>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="H14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="25">
+        <f>+ROUND(I13,)</f>
+        <v>495</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="F15" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="8"/>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H15" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="8"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B16" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="52"/>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B16" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="55"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
     </row>
-    <row r="17" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" s="48">
         <v>1100.05</v>
       </c>
       <c r="D17" s="4"/>
-      <c r="F17" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17" s="51"/>
-      <c r="H17" s="52"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="H17" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="55"/>
+      <c r="J17" s="56"/>
     </row>
-    <row r="18" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C18" s="49">
         <f>+(C8-C17)*C13*C6</f>
-        <v>82017500.000000119</v>
+        <v>65691375.000000097</v>
       </c>
       <c r="D18" s="8"/>
-      <c r="F18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="48">
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="H18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="48">
         <v>1100.05</v>
       </c>
-      <c r="H18" s="4"/>
+      <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
       <c r="D19" s="20"/>
-      <c r="F19" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19" s="49">
-        <f>+(G8-G18)*G14*G6</f>
-        <v>57257500.000000082</v>
-      </c>
-      <c r="H19" s="8"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="H19" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I19" s="49">
+        <f>+(I8-I18)*I14*I6</f>
+        <v>38300625.000000052</v>
+      </c>
+      <c r="J19" s="8"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
       <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
       <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
       <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
       <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B16:D16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>